--- a/product_upload/packages/57/file.xlsx
+++ b/product_upload/packages/57/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -829,6 +834,11 @@
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
+        <is>
+          <t>Docrosa</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
         <is>
           <t>SKU-CC9A9159E4B5</t>
         </is>
@@ -849,7 +859,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1009,6 +1019,11 @@
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
+        <is>
+          <t>Docrosa</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
         <is>
           <t>SKU-786EB641EBD1</t>
         </is>
@@ -1029,7 +1044,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1185,6 +1200,11 @@
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="inlineStr">
+        <is>
+          <t>Omeprex Plus</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
         <is>
           <t>SKU-A62631F45F67</t>
         </is>
@@ -1205,7 +1225,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1367,6 +1387,11 @@
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
+        <is>
+          <t>Elbag</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
         <is>
           <t>SKU-02BFFCF80828</t>
         </is>
@@ -1387,7 +1412,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1553,6 +1578,11 @@
         </is>
       </c>
       <c r="AT6" t="inlineStr">
+        <is>
+          <t>Elbag</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
         <is>
           <t>SKU-E1D5F887737F</t>
         </is>
@@ -1573,7 +1603,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1733,6 +1763,11 @@
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
+        <is>
+          <t>PANTOL</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
         <is>
           <t>SKU-F0D60862FBE3</t>
         </is>
@@ -1753,7 +1788,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1919,6 +1954,11 @@
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
+        <is>
+          <t>Aprolin</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>SKU-777624063FE9</t>
         </is>
@@ -1939,7 +1979,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2109,6 +2149,11 @@
         </is>
       </c>
       <c r="AT9" t="inlineStr">
+        <is>
+          <t>Aprolin</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
         <is>
           <t>SKU-F6B4EEAF920F</t>
         </is>
@@ -2129,7 +2174,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2291,6 +2336,11 @@
         </is>
       </c>
       <c r="AT10" t="inlineStr">
+        <is>
+          <t>Rezurock</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
         <is>
           <t>SKU-2832D74CEE1E</t>
         </is>
@@ -2311,7 +2361,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2473,6 +2523,11 @@
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
+        <is>
+          <t>Ultasil</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
         <is>
           <t>SKU-A732C338E5BD</t>
         </is>
@@ -2493,7 +2548,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2659,6 +2714,11 @@
         </is>
       </c>
       <c r="AT12" t="inlineStr">
+        <is>
+          <t>Ultasil</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
         <is>
           <t>SKU-8F0EBE9F2626</t>
         </is>
@@ -2679,7 +2739,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2841,6 +2901,11 @@
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
+        <is>
+          <t>Ultasil</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
         <is>
           <t>SKU-8D8BB350A6FF</t>
         </is>
@@ -2861,7 +2926,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3033,6 +3098,11 @@
         </is>
       </c>
       <c r="AT14" t="inlineStr">
+        <is>
+          <t>Nuvessa</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
         <is>
           <t>SKU-93CB8E0DE87B</t>
         </is>
@@ -3053,7 +3123,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3221,6 +3291,11 @@
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
+        <is>
+          <t>Concentia</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
         <is>
           <t>SKU-AB16D544C0AF</t>
         </is>
@@ -3241,7 +3316,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3409,6 +3484,11 @@
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
+        <is>
+          <t>Concentia</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
         <is>
           <t>SKU-F8767E5BBF08</t>
         </is>
@@ -3429,7 +3509,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3603,6 +3683,11 @@
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
+        <is>
+          <t>Mictonorm XL</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
         <is>
           <t>SKU-716CCDBD9393</t>
         </is>
@@ -3623,7 +3708,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3789,6 +3874,11 @@
         </is>
       </c>
       <c r="AT18" t="inlineStr">
+        <is>
+          <t>Trovapt</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
         <is>
           <t>SKU-94032A9593F0</t>
         </is>
@@ -3809,7 +3899,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3975,6 +4065,11 @@
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
+        <is>
+          <t>Levogand</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
         <is>
           <t>SKU-8CBE30470B80</t>
         </is>
@@ -3995,7 +4090,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4161,6 +4256,11 @@
         </is>
       </c>
       <c r="AT20" t="inlineStr">
+        <is>
+          <t>Sita</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
         <is>
           <t>SKU-59B89A527448</t>
         </is>
@@ -4181,7 +4281,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4339,6 +4439,11 @@
       <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
+        <is>
+          <t>Sita</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>SKU-DDCC107181F9</t>
         </is>
@@ -4359,7 +4464,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4519,6 +4624,11 @@
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
+        <is>
+          <t>PROVINDA PLUS</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
         <is>
           <t>SKU-8C4E39FC1929</t>
         </is>
@@ -4539,7 +4649,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4703,6 +4813,11 @@
         </is>
       </c>
       <c r="AT23" t="inlineStr">
+        <is>
+          <t>PROVINDA PLUS</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
         <is>
           <t>SKU-DF8EF7474834</t>
         </is>
@@ -4723,7 +4838,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4879,6 +4994,11 @@
       <c r="AR24" t="inlineStr"/>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
+        <is>
+          <t>PROVINDA PLUS</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
         <is>
           <t>SKU-C1CFD1E964D0</t>
         </is>
@@ -4899,7 +5019,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5061,6 +5181,11 @@
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
+        <is>
+          <t>PROVINDA PLUS</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
         <is>
           <t>SKU-3F8E60FE7870</t>
         </is>
@@ -5081,7 +5206,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5251,6 +5376,11 @@
         </is>
       </c>
       <c r="AT26" t="inlineStr">
+        <is>
+          <t>Malaquon</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
         <is>
           <t>SKU-4ECB04BC45D6</t>
         </is>
@@ -5271,7 +5401,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5441,6 +5571,11 @@
         </is>
       </c>
       <c r="AT27" t="inlineStr">
+        <is>
+          <t>Malaquon</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
         <is>
           <t>SKU-D1DC8ECEA5FA</t>
         </is>
@@ -5461,7 +5596,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5629,6 +5764,11 @@
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
+        <is>
+          <t>TACROZ Forte</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
         <is>
           <t>SKU-B0DF6116A7C8</t>
         </is>
@@ -5649,7 +5789,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5821,6 +5961,11 @@
         </is>
       </c>
       <c r="AT29" t="inlineStr">
+        <is>
+          <t>Tacroz</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
         <is>
           <t>SKU-608E85B4F9B6</t>
         </is>
@@ -5841,7 +5986,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6001,6 +6146,11 @@
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
+        <is>
+          <t>Ligra</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
         <is>
           <t>SKU-113862C146F9</t>
         </is>
@@ -6021,7 +6171,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6179,6 +6329,11 @@
       <c r="AR31" t="inlineStr"/>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
+        <is>
+          <t>Tulepsy</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
         <is>
           <t>SKU-FD8854DB84A8</t>
         </is>
@@ -6199,7 +6354,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6359,6 +6514,11 @@
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
+        <is>
+          <t>SITAVIA</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
         <is>
           <t>SKU-DAF756D90B7B</t>
         </is>
@@ -6379,7 +6539,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6543,6 +6703,11 @@
         </is>
       </c>
       <c r="AT33" t="inlineStr">
+        <is>
+          <t>SITAVIA</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
         <is>
           <t>SKU-D39564A14CB5</t>
         </is>
@@ -6563,7 +6728,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6720,6 +6885,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>Tymlos</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-9D437B2F9C04</t>
         </is>
       </c>
@@ -6739,7 +6909,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6910,6 +7080,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Mounjaro KwikPen</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-BBF48073BBCB</t>
         </is>
       </c>
@@ -6929,7 +7104,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7104,6 +7279,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Mounjaro KwikPen</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-393EC03F41AC</t>
         </is>
       </c>
@@ -7123,7 +7303,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7298,6 +7478,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>Mounjaro KwikPen</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-CA77BF757D6B</t>
         </is>
       </c>
@@ -7317,7 +7502,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7492,6 +7677,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>Mounjaro KwikPen</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-44ECF704D21D</t>
         </is>
       </c>
@@ -7511,7 +7701,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7682,6 +7872,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>Mounjaro KwikPen</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-9C20BDE48A88</t>
         </is>
       </c>
@@ -7701,7 +7896,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7872,6 +8067,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Mounjaro KwikPen</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-6FDAEEB0BFDA</t>
         </is>
       </c>
@@ -7891,7 +8091,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8057,6 +8257,11 @@
       <c r="AR41" t="inlineStr"/>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
+        <is>
+          <t>Empagliflozin SPC</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
         <is>
           <t>SKU-FB45F7500598</t>
         </is>
@@ -8077,7 +8282,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8247,6 +8452,11 @@
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
+        <is>
+          <t>Empagliflozin SPC</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
         <is>
           <t>SKU-BDC1B55B6E42</t>
         </is>
@@ -8267,7 +8477,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8433,6 +8643,11 @@
       <c r="AR43" t="inlineStr"/>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> BLUM D</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
         <is>
           <t>SKU-DB8284551FA0</t>
         </is>
@@ -8453,7 +8668,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8611,6 +8826,11 @@
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
+        <is>
+          <t>Rosol</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
         <is>
           <t>SKU-9523DFBAEE6A</t>
         </is>
@@ -8631,7 +8851,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8795,6 +9015,11 @@
         </is>
       </c>
       <c r="AT45" t="inlineStr">
+        <is>
+          <t>Tralix</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
         <is>
           <t>SKU-ED792976E95B</t>
         </is>
@@ -8815,7 +9040,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8975,6 +9200,11 @@
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
+        <is>
+          <t>UNITUM</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
         <is>
           <t>SKU-47E1B9FD2995</t>
         </is>
@@ -8995,7 +9225,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9159,6 +9389,11 @@
         </is>
       </c>
       <c r="AT47" t="inlineStr">
+        <is>
+          <t>Atorva</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
         <is>
           <t>SKU-5CDCB33A8FD8</t>
         </is>
@@ -9179,7 +9414,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9339,6 +9574,11 @@
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
+        <is>
+          <t>Atorva</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
         <is>
           <t>SKU-757A8CEB90F4</t>
         </is>
@@ -9359,7 +9599,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9523,6 +9763,11 @@
         </is>
       </c>
       <c r="AT49" t="inlineStr">
+        <is>
+          <t>Aripro</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
         <is>
           <t>SKU-C1EC0777C70F</t>
         </is>
@@ -9543,7 +9788,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9703,6 +9948,11 @@
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
+        <is>
+          <t>Brimo-P</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
         <is>
           <t>SKU-EE51F79573D5</t>
         </is>
@@ -9723,7 +9973,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9883,6 +10133,11 @@
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
+        <is>
+          <t>Ortyka</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
         <is>
           <t>SKU-EA671CA7C906</t>
         </is>
@@ -9903,7 +10158,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10067,6 +10322,11 @@
         </is>
       </c>
       <c r="AT52" t="inlineStr">
+        <is>
+          <t>sirolimus</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
         <is>
           <t>SKU-D056B09E9884</t>
         </is>
@@ -10087,7 +10347,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10247,6 +10507,11 @@
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
+        <is>
+          <t>ORS</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
         <is>
           <t>SKU-24DB907DDBBB</t>
         </is>
@@ -10267,7 +10532,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10427,6 +10692,11 @@
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
+        <is>
+          <t>Pratima Duo</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
         <is>
           <t>SKU-D2A0155F0985</t>
         </is>
@@ -10447,7 +10717,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10611,6 +10881,11 @@
         </is>
       </c>
       <c r="AT55" t="inlineStr">
+        <is>
+          <t>Pratima Duo</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
         <is>
           <t>SKU-3E1216CF6A4C</t>
         </is>
@@ -10631,7 +10906,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10787,6 +11062,11 @@
       <c r="AR56" t="inlineStr"/>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="inlineStr">
+        <is>
+          <t>Pratima Duo</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
         <is>
           <t>SKU-49CBB589A277</t>
         </is>
@@ -10807,7 +11087,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10967,6 +11247,11 @@
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
+        <is>
+          <t>Pratima Duo</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
         <is>
           <t>SKU-8C06F22C68DF</t>
         </is>
@@ -10987,7 +11272,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11147,6 +11432,11 @@
         </is>
       </c>
       <c r="AT58" t="inlineStr">
+        <is>
+          <t>Potassium Chloride Extended-Release Tablets USP</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
         <is>
           <t>SKU-60FBCD42AB3F</t>
         </is>
@@ -11167,7 +11457,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11337,6 +11627,11 @@
         </is>
       </c>
       <c r="AT59" t="inlineStr">
+        <is>
+          <t>Posazox</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
         <is>
           <t>SKU-2010C85E77E4</t>
         </is>
@@ -11357,7 +11652,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11535,6 +11830,11 @@
         </is>
       </c>
       <c r="AT60" t="inlineStr">
+        <is>
+          <t>Uridisitol</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
         <is>
           <t>SKU-1ABD712E53D7</t>
         </is>
@@ -11555,7 +11855,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11721,6 +12021,11 @@
         </is>
       </c>
       <c r="AT61" t="inlineStr">
+        <is>
+          <t>Mofecon-DR</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
         <is>
           <t>SKU-6F2DD0491632</t>
         </is>
@@ -11741,7 +12046,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11907,6 +12212,11 @@
         </is>
       </c>
       <c r="AT62" t="inlineStr">
+        <is>
+          <t>Mofecon-DR</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
         <is>
           <t>SKU-FAB9FA0F3289</t>
         </is>
@@ -11927,7 +12237,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12093,6 +12403,11 @@
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
+        <is>
+          <t>Prestoprix Plus</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
         <is>
           <t>SKU-3FCEE4DB3BEF</t>
         </is>
@@ -12113,7 +12428,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12283,6 +12598,11 @@
         </is>
       </c>
       <c r="AT64" t="inlineStr">
+        <is>
+          <t>Prestoprix Plus</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
         <is>
           <t>SKU-136EEAD97B24</t>
         </is>
@@ -12303,7 +12623,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12456,6 +12776,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>ROCLANDA</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-BD1ADCC8E22F</t>
         </is>
       </c>
@@ -12475,7 +12800,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12635,6 +12960,11 @@
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
+        <is>
+          <t>Siromune</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
         <is>
           <t>SKU-06E694938718</t>
         </is>
@@ -12655,7 +12985,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12815,6 +13145,11 @@
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
+        <is>
+          <t>Conestal</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
         <is>
           <t>SKU-AB3EE98471AB</t>
         </is>
@@ -12835,7 +13170,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12999,6 +13334,11 @@
         </is>
       </c>
       <c r="AT68" t="inlineStr">
+        <is>
+          <t>Conestal</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
         <is>
           <t>SKU-9D8D763B53BE</t>
         </is>
@@ -13019,7 +13359,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13193,6 +13533,11 @@
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
+        <is>
+          <t>Sapropterin Amarox</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
         <is>
           <t>SKU-674DFE04989B</t>
         </is>
@@ -13213,7 +13558,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13379,6 +13724,11 @@
         </is>
       </c>
       <c r="AT70" t="inlineStr">
+        <is>
+          <t>Sapropterin Amarox</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
         <is>
           <t>SKU-BB8518BA4E4C</t>
         </is>
@@ -13399,7 +13749,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13561,6 +13911,11 @@
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
+        <is>
+          <t>Sapropterin Amarox</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
         <is>
           <t>SKU-F139B92F1CE0</t>
         </is>
@@ -13581,7 +13936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13747,6 +14102,11 @@
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
+        <is>
+          <t>Rufzel</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
         <is>
           <t>SKU-BAE510CFC815</t>
         </is>
@@ -13767,7 +14127,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13933,6 +14293,11 @@
         </is>
       </c>
       <c r="AT73" t="inlineStr">
+        <is>
+          <t>Gliptus</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
         <is>
           <t>SKU-60A5FAC4645A</t>
         </is>
@@ -13953,7 +14318,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14119,6 +14484,11 @@
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
+        <is>
+          <t>Erelzi</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
         <is>
           <t>SKU-AF8E0E426B2D</t>
         </is>
@@ -14139,7 +14509,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14309,6 +14679,11 @@
         </is>
       </c>
       <c r="AT75" t="inlineStr">
+        <is>
+          <t>Erelzi</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
         <is>
           <t>SKU-F18EB771CE72</t>
         </is>
@@ -14329,7 +14704,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14495,6 +14870,11 @@
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
+        <is>
+          <t>Erelzi</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
         <is>
           <t>SKU-C00DCFED47D7</t>
         </is>
@@ -14515,7 +14895,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14679,6 +15059,11 @@
         </is>
       </c>
       <c r="AT77" t="inlineStr">
+        <is>
+          <t>Abiraterone Acetate Neapolis</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
         <is>
           <t>SKU-8AABB49825CE</t>
         </is>
@@ -14699,7 +15084,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14857,6 +15242,11 @@
       <c r="AR78" t="inlineStr"/>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
+        <is>
+          <t>Redex</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
         <is>
           <t>SKU-2486D1FDBC17</t>
         </is>
@@ -14877,7 +15267,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15047,6 +15437,11 @@
       <c r="AR79" t="inlineStr"/>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
+        <is>
+          <t>Prestoprix Plus</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
         <is>
           <t>SKU-24FCAAA16895</t>
         </is>
@@ -15067,7 +15462,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15245,6 +15640,11 @@
         </is>
       </c>
       <c r="AT80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Mictonorm XL</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
         <is>
           <t>SKU-38E92464A46C</t>
         </is>
@@ -15265,7 +15665,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15425,6 +15825,11 @@
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
+        <is>
+          <t>Gripdi</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
         <is>
           <t>SKU-309251980D0B</t>
         </is>
@@ -15445,7 +15850,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15609,6 +16014,11 @@
         </is>
       </c>
       <c r="AT82" t="inlineStr">
+        <is>
+          <t>Gripdi</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
         <is>
           <t>SKU-4939B83BBE7B</t>
         </is>
@@ -15629,7 +16039,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15797,6 +16207,11 @@
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
+        <is>
+          <t>Litfulo</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
         <is>
           <t>SKU-B2117F4E422D</t>
         </is>
@@ -15817,7 +16232,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15983,6 +16398,11 @@
         </is>
       </c>
       <c r="AT84" t="inlineStr">
+        <is>
+          <t>Atomibe</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
         <is>
           <t>SKU-D161C1A8AE01</t>
         </is>
@@ -16003,7 +16423,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16169,6 +16589,11 @@
         </is>
       </c>
       <c r="AT85" t="inlineStr">
+        <is>
+          <t>Atomibe</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
         <is>
           <t>SKU-FD2D43F7CEF2</t>
         </is>
@@ -16189,7 +16614,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16351,6 +16776,11 @@
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
+        <is>
+          <t>Atomibe</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
         <is>
           <t>SKU-67941020C30A</t>
         </is>
@@ -16371,7 +16801,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16531,6 +16961,11 @@
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
+        <is>
+          <t>DASATINIB NEAPOLIS</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
         <is>
           <t>SKU-3C3BF9E19E36</t>
         </is>
@@ -16551,7 +16986,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16713,6 +17148,11 @@
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
+        <is>
+          <t>Matroda</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
         <is>
           <t>SKU-1B76DFC3052D</t>
         </is>
@@ -16733,7 +17173,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16897,6 +17337,11 @@
         </is>
       </c>
       <c r="AT89" t="inlineStr">
+        <is>
+          <t>Matroda</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
         <is>
           <t>SKU-941195E54763</t>
         </is>
@@ -16917,7 +17362,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17081,6 +17526,11 @@
         </is>
       </c>
       <c r="AT90" t="inlineStr">
+        <is>
+          <t>Sitavic</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
         <is>
           <t>SKU-13A8534652F6</t>
         </is>
@@ -17101,7 +17551,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17265,6 +17715,11 @@
         </is>
       </c>
       <c r="AT91" t="inlineStr">
+        <is>
+          <t>Sitavic</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
         <is>
           <t>SKU-CD67A8E17F42</t>
         </is>
@@ -17285,7 +17740,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17447,6 +17902,11 @@
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
+        <is>
+          <t>Penovar</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
         <is>
           <t>SKU-A8CB82E8DAE9</t>
         </is>
@@ -17467,7 +17927,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17629,6 +18089,11 @@
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
+        <is>
+          <t>Tavlesse</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
         <is>
           <t>SKU-5E6970985D74</t>
         </is>
@@ -17649,7 +18114,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17811,6 +18276,11 @@
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
+        <is>
+          <t>Tavlesse</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
         <is>
           <t>SKU-5BA59FECED2C</t>
         </is>
@@ -17831,7 +18301,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18005,6 +18475,11 @@
         </is>
       </c>
       <c r="AT95" t="inlineStr">
+        <is>
+          <t>Saventi</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
         <is>
           <t>SKU-8A83ABFD7955</t>
         </is>
@@ -18025,7 +18500,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18199,6 +18674,11 @@
         </is>
       </c>
       <c r="AT96" t="inlineStr">
+        <is>
+          <t>Saventi</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
         <is>
           <t>SKU-AD822C5CC76C</t>
         </is>
@@ -18219,7 +18699,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18393,6 +18873,11 @@
         </is>
       </c>
       <c r="AT97" t="inlineStr">
+        <is>
+          <t>Saventi</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
         <is>
           <t>SKU-26F8DF4521DB</t>
         </is>
@@ -18413,7 +18898,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18579,6 +19064,11 @@
         </is>
       </c>
       <c r="AT98" t="inlineStr">
+        <is>
+          <t>Cetraxal plus</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
         <is>
           <t>SKU-749057DE13D1</t>
         </is>
@@ -18599,7 +19089,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18773,6 +19263,11 @@
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
+        <is>
+          <t>Prestoprix</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
         <is>
           <t>SKU-6D877E83686B</t>
         </is>
@@ -18793,7 +19288,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18971,6 +19466,11 @@
         </is>
       </c>
       <c r="AT100" t="inlineStr">
+        <is>
+          <t>Prestoprix</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
         <is>
           <t>SKU-38B6A6D63A6F</t>
         </is>
@@ -18991,7 +19491,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19151,6 +19651,11 @@
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Cimuquit</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-E938A3AF9C03</t>
         </is>
@@ -19167,7 +19672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19213,100 +19718,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19338,7 +19848,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19353,92 +19863,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-37318</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>181.49</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>563</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19470,7 +19985,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19485,92 +20000,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-66529</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>69.17</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>564</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19602,7 +20122,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19617,92 +20137,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-68316</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>442.03</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>565</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19734,7 +20259,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19749,92 +20274,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-93231</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>67.51000000000001</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>566</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19866,7 +20396,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19881,92 +20411,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-84125</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>179.92</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>567</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19998,7 +20533,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20013,92 +20548,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-78503</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>268.04</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>568</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20130,7 +20670,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20145,92 +20685,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-76945</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>71.95</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>569</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20262,7 +20807,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20277,92 +20822,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-20523</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>322.95</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>570</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20394,7 +20944,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20409,92 +20959,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-45892</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>434.41</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>571</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20526,7 +21081,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20541,92 +21096,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-94111</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>94.7</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>572</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20658,7 +21218,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20673,92 +21233,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-68483</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>252.38</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>573</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20775,7 +21340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20881,6 +21446,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20916,7 +21491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20981,6 +21556,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-1B42E898A02B</t>
         </is>
@@ -21017,7 +21602,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21082,6 +21667,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-CDA3C0BF23FB</t>
         </is>
@@ -21118,7 +21713,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21183,6 +21778,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-90532D57057C</t>
         </is>
@@ -21219,7 +21824,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21284,6 +21889,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-27BCF8B975E2</t>
         </is>
@@ -21320,7 +21935,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21385,6 +22000,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-2F0F7A0FE850</t>
         </is>
@@ -21421,7 +22046,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21486,6 +22111,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-BC8E6AD359BE</t>
         </is>
@@ -21522,7 +22157,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21587,6 +22222,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-C595F4FB35E9</t>
         </is>
@@ -21623,7 +22268,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21688,6 +22333,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-0C93EDBBE2F6</t>
         </is>
@@ -21724,7 +22379,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21789,6 +22444,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-156FFBBF8586</t>
         </is>
@@ -21825,7 +22490,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21890,6 +22555,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-63BD8DC16EFF</t>
         </is>
@@ -21926,7 +22601,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21991,6 +22666,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-75356FE31A2B</t>
         </is>
@@ -22027,7 +22712,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22092,6 +22777,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-BF7971781C3E</t>
         </is>
@@ -22128,7 +22823,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22193,6 +22888,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-827465FFFBE4</t>
         </is>
@@ -22229,7 +22934,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22294,6 +22999,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-5ECE9118CA50</t>
         </is>
@@ -22330,7 +23045,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22395,6 +23110,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-0163F287B208</t>
         </is>
@@ -22431,7 +23156,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22496,6 +23221,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-3BDC30E8B3C5</t>
         </is>
@@ -22532,7 +23267,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22597,6 +23332,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-2017BD2B06A6</t>
         </is>
@@ -22633,7 +23378,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22698,6 +23443,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-085ED94C8666</t>
         </is>
@@ -22734,7 +23489,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22799,6 +23554,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-46D1715D9321</t>
         </is>
@@ -22835,7 +23600,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22900,6 +23665,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-AF1466FEFF5A</t>
         </is>

--- a/product_upload/packages/57/file.xlsx
+++ b/product_upload/packages/57/file.xlsx
@@ -682,8 +682,16 @@
           <t>1282182443-545-909341096770</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Docrosa</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Docrosa detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -867,8 +875,16 @@
           <t>8188500638-036-057410443692</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Docrosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Docrosa detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1052,8 +1068,16 @@
           <t>0983133234-972-402850120721</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Omeprex Plus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Omeprex Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1233,8 +1257,16 @@
           <t>8732781445-305-661182563951</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Elbag</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Elbag detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1420,8 +1452,16 @@
           <t>3892955683-390-112113334148</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Elbag</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Elbag detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1611,8 +1651,16 @@
           <t>9009305692-714-628934808912</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PANTOL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>PANTOL detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1796,8 +1844,16 @@
           <t>5209180963-145-100712137695</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aprolin</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Aprolin detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1987,8 +2043,16 @@
           <t>1316493008-534-231957743090</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aprolin</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Aprolin detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2182,8 +2246,16 @@
           <t>8783778925-800-076818487218</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rezurock</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Rezurock detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2369,8 +2441,16 @@
           <t>6704147364-371-628980666284</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ultasil</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ultasil detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2556,8 +2636,16 @@
           <t>3380217057-471-480514969006</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ultasil</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Ultasil detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2747,8 +2835,16 @@
           <t>6381329528-982-991969609034</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ultasil</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Ultasil detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3716,8 +3812,16 @@
           <t>5449371428-549-865494008298</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Trovapt</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Trovapt detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3907,8 +4011,16 @@
           <t>7815309770-836-052500556717</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Levogand</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Levogand detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4098,8 +4210,16 @@
           <t>3774592359-846-578793618989</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sita</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sita detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4289,8 +4409,16 @@
           <t>7840601650-402-084040717081</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sita</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sita detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4472,8 +4600,16 @@
           <t>4835063032-298-270733944606</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROVINDA PLUS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>PROVINDA PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4657,8 +4793,16 @@
           <t>2922340055-993-306835497186</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROVINDA PLUS</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>PROVINDA PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4846,8 +4990,16 @@
           <t>4113335158-550-467748390313</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROVINDA PLUS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>PROVINDA PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -5027,8 +5179,16 @@
           <t>5506425815-464-670099885078</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROVINDA PLUS</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>PROVINDA PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5214,8 +5374,16 @@
           <t>4671654962-162-088229694187</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Malaquon</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Malaquon detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5409,8 +5577,16 @@
           <t>2661971932-614-980999553098</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Malaquon</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Malaquon detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5994,8 +6170,16 @@
           <t>4879154339-336-750724582119</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ligra</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Ligra detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6179,8 +6363,16 @@
           <t>0392152172-564-903223608169</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tulepsy</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Tulepsy detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6362,8 +6554,16 @@
           <t>1359878059-014-354180605586</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SITAVIA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>SITAVIA detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6547,8 +6747,16 @@
           <t>0458327911-398-044225929375</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SITAVIA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>SITAVIA detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6736,8 +6944,16 @@
           <t>9863064328-769-623074833834</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tymlos</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Tymlos detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -8676,8 +8892,16 @@
           <t>1460442844-394-269291679111</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rosol</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Rosol detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8859,8 +9083,16 @@
           <t>9328819592-607-771149492959</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tralix</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Tralix detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -9048,8 +9280,16 @@
           <t>3037474601-200-256182792471</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ UNITUM</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>UNITUM detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9233,8 +9473,16 @@
           <t>0609683537-450-076452455465</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Atorva</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Atorva detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9422,8 +9670,16 @@
           <t>8566245127-886-709955404154</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Atorva</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Atorva detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9607,8 +9863,16 @@
           <t>7157967921-473-167015555243</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aripro</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Aripro detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9796,8 +10060,16 @@
           <t>8655106635-694-594652864852</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Brimo-P</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Brimo-P detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9981,8 +10253,16 @@
           <t>5332462682-519-076525360080</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ortyka</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Ortyka detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10166,8 +10446,16 @@
           <t>2620296337-741-425603468028</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ sirolimus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>sirolimus detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10355,8 +10643,16 @@
           <t>6241827218-521-521805197380</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ORS</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ORS detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10540,8 +10836,16 @@
           <t>2499253849-135-603749615252</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pratima Duo</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Pratima Duo detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10725,8 +11029,16 @@
           <t>3265944639-492-053623101564</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pratima Duo</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Pratima Duo detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10914,8 +11226,16 @@
           <t>8737229029-893-157462549170</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pratima Duo</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Pratima Duo detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -11095,8 +11415,16 @@
           <t>4304464277-281-692062021891</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Pratima Duo</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Pratima Duo detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11280,8 +11608,16 @@
           <t>7119974443-748-996250219037</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Potassium Chloride Extended-Release Tablets USP</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Potassium Chloride Extended-Release Tablets USP detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
@@ -11465,8 +11801,16 @@
           <t>1603052149-191-395717584598</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Posazox</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Posazox detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11863,8 +12207,16 @@
           <t>6247690695-074-324121864291</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Mofecon-DR</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Mofecon-DR detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -12054,8 +12406,16 @@
           <t>5854580898-774-765674038479</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Mofecon-DR</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Mofecon-DR detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -12245,8 +12605,16 @@
           <t>6482941237-751-513093391627</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Prestoprix Plus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Prestoprix Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12436,8 +12804,16 @@
           <t>4396497754-100-098437135606</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Prestoprix Plus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Prestoprix Plus detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12631,8 +13007,16 @@
           <t>5776970902-327-281664979770</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROCLANDA</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>ROCLANDA detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -12808,8 +13192,16 @@
           <t>7604644348-149-742199089463</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Siromune</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Siromune detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12993,8 +13385,16 @@
           <t>7167200017-958-019977495533</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Conestal</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Conestal detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13178,8 +13578,16 @@
           <t>4854198087-866-191473366335</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Conestal</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Conestal detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13566,8 +13974,16 @@
           <t>1898761405-673-057854233001</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sapropterin Amarox</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Sapropterin Amarox detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13757,8 +14173,16 @@
           <t>4864952607-498-855416652633</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sapropterin Amarox</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sapropterin Amarox detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -13944,8 +14368,16 @@
           <t>1775525682-364-553979744072</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rufzel</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Rufzel detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14135,8 +14567,16 @@
           <t>1841052675-333-806474806328</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Gliptus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Gliptus detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14326,8 +14766,16 @@
           <t>4143837804-955-491719307077</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erelzi</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Erelzi detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14517,8 +14965,16 @@
           <t>0968709408-814-913882700424</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erelzi</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Erelzi detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14712,8 +15168,16 @@
           <t>0921111806-488-883879336016</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erelzi</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Erelzi detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14903,8 +15367,16 @@
           <t>6107999736-743-557463029976</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Abiraterone Acetate Neapolis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Abiraterone Acetate Neapolis detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15092,8 +15564,16 @@
           <t>7692726611-813-055207262345</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Redex</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Redex detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -15673,8 +16153,16 @@
           <t>0434373266-643-730887934891</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Gripdi</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Gripdi detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15858,8 +16346,16 @@
           <t>4726610214-829-303782637012</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Gripdi</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Gripdi detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16240,8 +16736,16 @@
           <t>1270730110-768-413783546090</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Atomibe</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Atomibe detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16431,8 +16935,16 @@
           <t>9317591395-039-005267786149</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Atomibe</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Atomibe detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16622,8 +17134,16 @@
           <t>7882072790-903-394782912220</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Atomibe</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Atomibe detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16809,8 +17329,16 @@
           <t>1480398814-721-673072767252</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DASATINIB NEAPOLIS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>DASATINIB NEAPOLIS detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16994,8 +17522,16 @@
           <t>8425889939-671-745810653167</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Matroda</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Matroda detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -17181,8 +17717,16 @@
           <t>4693759586-407-566110590343</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Matroda</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Matroda detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17370,8 +17914,16 @@
           <t>6095377318-032-846513590641</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sitavic</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sitavic detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17559,8 +18111,16 @@
           <t>0805316627-820-713591976618</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sitavic</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sitavic detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17748,8 +18308,16 @@
           <t>7333257494-108-825237744801</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Penovar</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Penovar detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17935,8 +18503,16 @@
           <t>8521605182-914-362390084540</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tavlesse</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Tavlesse detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18122,8 +18698,16 @@
           <t>3945522956-256-422372582286</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tavlesse</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Tavlesse detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -18906,8 +19490,16 @@
           <t>8455912224-625-065025587484</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cetraxal plus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Cetraxal plus detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -19499,8 +20091,16 @@
           <t>2075918959-146-968592706197</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cimuquit</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Cimuquit detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/57/file.xlsx
+++ b/product_upload/packages/57/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20318,7 +20318,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21940,7 +21940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22021,40 +22021,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22134,38 +22139,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>350.96</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-1B42E898A02B</t>
         </is>
@@ -22245,38 +22255,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>404.13</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-CDA3C0BF23FB</t>
         </is>
@@ -22356,38 +22371,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>65.61</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-90532D57057C</t>
         </is>
@@ -22467,38 +22487,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>190.34</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-27BCF8B975E2</t>
         </is>
@@ -22578,38 +22603,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>161.11</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-2F0F7A0FE850</t>
         </is>
@@ -22689,38 +22719,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>292.12</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-BC8E6AD359BE</t>
         </is>
@@ -22800,38 +22835,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>236.55</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-C595F4FB35E9</t>
         </is>
@@ -22911,38 +22951,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>81.72</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-0C93EDBBE2F6</t>
         </is>
@@ -23022,38 +23067,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>492.92</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-156FFBBF8586</t>
         </is>
@@ -23133,38 +23183,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>440.82</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-63BD8DC16EFF</t>
         </is>
@@ -23244,38 +23299,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>482.07</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-75356FE31A2B</t>
         </is>
@@ -23355,38 +23415,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>394.39</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-BF7971781C3E</t>
         </is>
@@ -23466,38 +23531,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>295.14</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-827465FFFBE4</t>
         </is>
@@ -23577,38 +23647,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>177.77</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-5ECE9118CA50</t>
         </is>
@@ -23688,38 +23763,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>58.95</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-0163F287B208</t>
         </is>
@@ -23799,38 +23879,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>88.88</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-3BDC30E8B3C5</t>
         </is>
@@ -23910,38 +23995,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>98.34999999999999</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-2017BD2B06A6</t>
         </is>
@@ -24021,38 +24111,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>232.12</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-085ED94C8666</t>
         </is>
@@ -24132,38 +24227,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>150.89</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-46D1715D9321</t>
         </is>
@@ -24243,38 +24343,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>187.81</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-AF1466FEFF5A</t>
         </is>
